--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/WISCONSIN_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/WISCONSIN_2021.xlsx
@@ -4434,7 +4434,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C227">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C236">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C579">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C668">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C703">
